--- a/Documents/Règlements/Règlements_2407.xlsx
+++ b/Documents/Règlements/Règlements_2407.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WpfProject\Gestcom\Documents\Règlements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB7091DC-35B5-4E11-90D1-976E87191126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11532533-FA01-4261-A2BF-9EA3F550244E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4128" yWindow="3396" windowWidth="17280" windowHeight="8964" activeTab="4" xr2:uid="{E8438AD5-D618-4187-BE1E-962F25C16FF8}"/>
+    <workbookView xWindow="4128" yWindow="3396" windowWidth="17280" windowHeight="8964" activeTab="4" xr2:uid="{F72C55A4-F06C-4B6F-B249-E4826208164A}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,7 +482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEB853C8-0AE1-49F3-8E8C-F4ED27618098}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6611A1BF-5FBA-4972-807F-A2E8F6839B63}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -489,8 +491,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD8B172-0DCF-44DF-B654-50731E5152D5}">
-  <dimension ref="D1:K2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA26F065-6DB3-4221-8719-599BF5B8BC82}">
+  <dimension ref="D1:K3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
@@ -499,7 +501,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:11" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:11" ht="18.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
@@ -509,14 +511,15 @@
       <c r="J2" s="3"/>
       <c r="K2" s="4"/>
     </row>
+    <row r="3" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF6DFDE-06D8-402D-A6C3-1039761A138D}">
-  <dimension ref="D1:K2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049D6991-96DE-4837-9F8A-22402CD56559}">
+  <dimension ref="D1:K3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
@@ -525,7 +528,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:11" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:11" ht="18.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
@@ -535,14 +538,15 @@
       <c r="J2" s="3"/>
       <c r="K2" s="4"/>
     </row>
+    <row r="3" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B7D9CE0-2265-401D-B46D-2D0A892AD74B}">
-  <dimension ref="D1:K2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB28E4B-DF63-4CDE-84B2-B7A8076AF859}">
+  <dimension ref="D1:K3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
@@ -551,7 +555,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:11" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:11" ht="18.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
@@ -561,14 +565,15 @@
       <c r="J2" s="3"/>
       <c r="K2" s="4"/>
     </row>
+    <row r="3" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A79831-B568-4F47-A403-E3D67C4A211C}">
-  <dimension ref="D1:K2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{548A25F5-E788-4F9A-BD62-986AA91F4426}">
+  <dimension ref="D1:K3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
@@ -577,7 +582,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:11" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:11" ht="18.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
@@ -587,6 +592,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="4"/>
     </row>
+    <row r="3" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Documents/Règlements/Règlements_2407.xlsx
+++ b/Documents/Règlements/Règlements_2407.xlsx
@@ -5,19 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WpfProject\Gestcom\Documents\Règlements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dossier Dev\Informatique\Gestcom\Documents\Règlements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11532533-FA01-4261-A2BF-9EA3F550244E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74D5AECE-ABE1-4BB0-AFDB-300267350744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4128" yWindow="3396" windowWidth="17280" windowHeight="8964" activeTab="4" xr2:uid="{F72C55A4-F06C-4B6F-B249-E4826208164A}"/>
+    <workbookView xWindow="-24390" yWindow="2685" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{B3A9F585-E32B-41BD-9CEA-128632DF79E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
-    <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
-    <sheet name="Feuil4" sheetId="4" r:id="rId4"/>
-    <sheet name="Feuil5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,19 +37,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>CLASSEMENT/REGLEMENT DE FABRICATION :</t>
   </si>
   <si>
     <t xml:space="preserve">     J A N V I E R     2 0 2 4</t>
+  </si>
+  <si>
+    <t>SOCIETES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    COLLECTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  PAINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   POIDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    QUALITE A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  %</t>
+  </si>
+  <si>
+    <t>QUAL.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    QUALITE B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    QUALITE C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   REGLEMENT</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PRIX</t>
+  </si>
+  <si>
+    <t>AU KG</t>
+  </si>
+  <si>
+    <t>MPN</t>
+  </si>
+  <si>
+    <t>Coef Valeur :</t>
+  </si>
+  <si>
+    <t>Marge</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCAF VILLEREVERSURE      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCAF BRESSE JURASSIENNE  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD COMBE CHATELEU        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IST GD COMBE CHATELEU    </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="###.##%"/>
+    <numFmt numFmtId="165" formatCode="###.##"/>
+    <numFmt numFmtId="166" formatCode="#\ ##0.00\ &quot;€&quot;"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,27 +126,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -94,8 +165,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF969696"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -106,18 +183,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -125,30 +202,78 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,117 +607,326 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6611A1BF-5FBA-4972-807F-A2E8F6839B63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{146FCD10-B058-42CC-BE19-E32779A1A153}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA26F065-6DB3-4221-8719-599BF5B8BC82}">
-  <dimension ref="D1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A90B27-367A-4DD1-9863-3FF6C2D57106}">
+  <dimension ref="B1:M18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.5546875" style="1"/>
+    <col min="2" max="2" width="27.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" style="1" customWidth="1"/>
+    <col min="6" max="8" width="10.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="1.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="1.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:11" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="4:11" ht="18.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:13" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:13" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049D6991-96DE-4837-9F8A-22402CD56559}">
-  <dimension ref="D1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.5546875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="4:11" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="4:11" ht="18.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB28E4B-DF63-4CDE-84B2-B7A8076AF859}">
-  <dimension ref="D1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.5546875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="4:11" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="4:11" ht="18.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{548A25F5-E788-4F9A-BD62-986AA91F4426}">
-  <dimension ref="D1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.5546875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="4:11" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="4:11" ht="18.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="4:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="2:13" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="11"/>
+      <c r="C5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="F7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="15" t="e">
+        <f>+M25/D7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="15" t="e">
+        <f>+(D7-M25)/D7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="18">
+        <v>500</v>
+      </c>
+      <c r="D11" s="19">
+        <v>6714</v>
+      </c>
+      <c r="E11" s="19">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18">
+        <f>D11-I11-K11</f>
+        <v>6714</v>
+      </c>
+      <c r="G11" s="20">
+        <f>ROUND(E11/C11*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>0</v>
+      </c>
+      <c r="I11" s="18">
+        <f>ROUND(+H11/$C11*$D11,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0</v>
+      </c>
+      <c r="K11" s="18">
+        <f>ROUND(+J11/$C11*$D11,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="21">
+        <v>358661.88</v>
+      </c>
+      <c r="M11" s="21">
+        <f>ROUND(L11/D11,2)</f>
+        <v>53.42</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="18">
+        <v>280</v>
+      </c>
+      <c r="D13" s="19">
+        <v>10449</v>
+      </c>
+      <c r="E13" s="19">
+        <v>0</v>
+      </c>
+      <c r="F13" s="18">
+        <f>D13-I13-K13</f>
+        <v>10449</v>
+      </c>
+      <c r="G13" s="20">
+        <f>ROUND(E13/C13*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="18">
+        <f>ROUND(+H13/$C13*$D13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="14">
+        <v>0</v>
+      </c>
+      <c r="K13" s="18">
+        <f>ROUND(+J13/$C13*$D13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="21">
+        <v>0</v>
+      </c>
+      <c r="M13" s="21">
+        <f>ROUND(L13/D13,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B15" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="18">
+        <v>96</v>
+      </c>
+      <c r="D15" s="19">
+        <v>3624</v>
+      </c>
+      <c r="E15" s="19">
+        <v>0</v>
+      </c>
+      <c r="F15" s="18">
+        <f>D15-I15-K15</f>
+        <v>3624</v>
+      </c>
+      <c r="G15" s="20">
+        <f>ROUND(E15/C15*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="18">
+        <f>ROUND(+H15/$C15*$D15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="14">
+        <v>0</v>
+      </c>
+      <c r="K15" s="18">
+        <f>ROUND(+J15/$C15*$D15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="21">
+        <v>0</v>
+      </c>
+      <c r="M15" s="21">
+        <f>ROUND(L15/D15,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B17" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="18">
+        <v>100</v>
+      </c>
+      <c r="D17" s="19">
+        <v>4000</v>
+      </c>
+      <c r="E17" s="19">
+        <v>0</v>
+      </c>
+      <c r="F17" s="18">
+        <f>D17-I17-K17</f>
+        <v>4000</v>
+      </c>
+      <c r="G17" s="20">
+        <f>ROUND(E17/C17*100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="18">
+        <f>ROUND(+H17/$C17*$D17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0</v>
+      </c>
+      <c r="K17" s="18">
+        <f>ROUND(+J17/$C17*$D17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="21">
+        <v>31200</v>
+      </c>
+      <c r="M17" s="21">
+        <f>ROUND(L17/D17,2)</f>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
